--- a/vault-dalarna-university/01 IIT/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Introfras.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$136</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +30,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -462,7 +469,3925 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BY1053</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper inom samhällsplanering, byggandets regelverk…</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1053</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>BY1056</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper inom värme- och fukttransport, ljudisoleri…</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1056</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BY1058</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-husmodell.…</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1058</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>BY1059</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall skaffa sig kunskaper om såväl teoretisk som praktisk träbyggnad…</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1059</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>BY1061</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet me kursen är att studenten ska skaffa sig kunskaper och färdigheter om systemuppbyggnad och funkt…</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1061</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BY1065</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att kursdeltagaren ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformati…</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1065</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BY2016</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>BY2022</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska uppnå förmåga att med helhetssyn självständigt och kreativt ident…</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BY2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>BY3001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Vid design av energieffektiva byggnader med hög nivå av komfort och hållbarhet krävs både en djup kunskap om detaljer so…</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BY3004</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen fokuserar på miljöklassningsverktyg för byggnader. Efter avslutad kurs ska studenterna kunna:…</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>GBY2GB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-modell.…</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>GBY2GC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformationsmo…</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GBY2GR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper inom fysisk planering med tyng…</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GBY2J2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska skaffa sig kunskaper…</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2J2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GBY2MA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om laster och krafter i byggkonstruktioner…</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GBY2MB</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper för att kunna organisera och genomföra pro…</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GBY2ME</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper i husbyggnadsteknik, speciellt beträffande…</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2ME</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GBY2NF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten skall tillägna sig kunskaper om laster och krafter i byggkonstruktioner samt gru…</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NF</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GBY2NG</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om byggandets organisation och genomförand…</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NG</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GBY2RX</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap och…</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RX</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GBY2V6</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig grundläggande kunskaper i arbetsplatsens organisat…</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>GBY2VR</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att öka medvetenheten om de hållbarhetsutmaningar som vi står inför. Kursen avser a…</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2VR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>GBY2XF</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper i husbyggnadsteknik, speciellt beträffande u…</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2XF</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>BFY224</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FYA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om vetenskapligt arbetssätt inom naturvetenskap …</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>BFY225</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FYA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY225</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>BFY226</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FYA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>BFY227</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FYA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>FY1018</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FYA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GFY345</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FYA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFY345</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>GIE26L</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26L</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GIE26M</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26M</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>GIE26N</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26N</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>GIE26P</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26P</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>GIE29N</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE29N</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>GIE2L7</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2L7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>GIE2MF</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2MF</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>GIE2QS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2QS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>GIE2RF</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>GIE3H2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>IE1068</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>IE1069</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1069</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>IE1076</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1076</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>IE2003</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': De allmänna målen med examensarbetet är att ge kursdeltagarna möjligheter att utveckla sin förmåga att inom ämnet indust…</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>AIK232</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GIK23M</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GIK289</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GIK299</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GIK2AL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GIK2BD</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2BD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>GIK2FB</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>GIK2JX</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>GIK2KM</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>GIK2LF</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2LF</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>GIK2NV</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>GIK2NX</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och…</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>GIK2PB</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>GIK2PD</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till nätverk, nätverkstjänster , nätverkssäkerhet, datakommunikati…</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PD</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GIK2PF</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GIK2PG</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GIK2QZ</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2QZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>GIK2UK</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>GIK2V4</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>GIK2XJ</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>GIK2XK</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XK</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>GIK2XZ</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>GIK2YK</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YK</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>GIK2YL</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YL</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>GIK2YN</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YN</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GIK2YP</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GIK2YR</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YR</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>GIK32J</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32J</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>GIK32K</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse _…</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32K</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GIK32L</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse _…</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32L</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>GIK32M</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse _…</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32M</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>GIK32N</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse _…</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32N</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>GIK339</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK339</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>GIK346</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK346</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>GIK347</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK347</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>GIK348</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK348</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>GIK34Y</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK34Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>GIK38G</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK38G</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>GIK38H</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK38H</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>IK1032</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska förvärva fördjupade kunskaper inom examensarbetets ämnesområde genom att u…</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>IK1064</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig utökade kunskaper i objektorienterad programmering och m…</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>IK1066</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper och färdigheter inom ämnesområdet geno…</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>GMA28W</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>MAA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska …</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>MA0011</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>MAA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>MA0013</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MAA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>MA1040</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MAA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska utveckla sin förmåga att förstå och använda matematiska begrepp o…</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1040</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>MA1042</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>MAA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig grundläggande teoretiska kunskaper i elementär a…</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>AMD238</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>AMD239</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana ämnes- och ämnesdidaktiska kunskaper som krävs för att i gru…</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>GMD2AR</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>GMD2GF</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>GMD2GG</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>GMD2TV</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>GMD2XQ</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>GMD33X</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>GMD33Y</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>MD2022</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet för kursen är att den studerande ska vidga och…</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>GMT343</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>GMT344</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT344</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>GMT349</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT349</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>GMT34R</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>GMT34W</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34W</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>MT1033</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter kursen kunna…</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>MT1074</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig kännedom om och förmåga till analys av de viktigas…</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>BEG222</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall ha nått en förtrogenhet med rådande forsknings- och utbildnings…</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>EG1012</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>EG2004</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>EG3019</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i …</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>EG3020</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>EG3022</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>EG4001</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa och väsentligen fördjupa sina kunskaper inom solenergitekni…</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GEG2UE</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>GEG2UL</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>GEG33B</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna ska efter avslutad kurs kunna:…</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>GSQ23J</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillämpa och fördjupa kunskaper och tekniker i databashantering…</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25F</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för …</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25J</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25N</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2H7</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar…</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2LA</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig…</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2PH</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2R5</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2Y2</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>SQ1003</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>AMI22Z</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>AMI23J</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>AMI27V</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>AMI295</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>GMI2C8</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa …</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>GMI2NW</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska behandla aktiviteter relaterade till automatiska programvarutest …</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2NW</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>GMI35R</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI35R</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E136"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/01 IIT/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -688,7 +688,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BY2025</t>
+          <t>BY3001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Vid design av energieffektiva byggnader med hög nivå av komfort och hållbarhet krävs både en djup kunskap om detaljer so…</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3001</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BY3001</t>
+          <t>BY3004</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Vid design av energieffektiva byggnader med hög nivå av komfort och hållbarhet krävs både en djup kunskap om detaljer so…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen fokuserar på miljöklassningsverktyg för byggnader. Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3004</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BY3004</t>
+          <t>GBY2GB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen fokuserar på miljöklassningsverktyg för byggnader. Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-modell.…</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GBY2GB</t>
+          <t>GBY2GC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-modell.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformationsmo…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GBY2GC</t>
+          <t>GBY2GR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformationsmo…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper inom fysisk planering med tyng…</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GBY2GR</t>
+          <t>GBY2J2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper inom fysisk planering med tyng…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska skaffa sig kunskaper…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2J2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GBY2J2</t>
+          <t>GBY2MA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska skaffa sig kunskaper…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om laster och krafter i byggkonstruktioner…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2J2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GBY2MA</t>
+          <t>GBY2MB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om laster och krafter i byggkonstruktioner…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper för att kunna organisera och genomföra pro…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MB</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GBY2MB</t>
+          <t>GBY2ME</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,19 +919,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper för att kunna organisera och genomföra pro…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper i husbyggnadsteknik, speciellt beträffande…</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2ME</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GBY2ME</t>
+          <t>GBY2NF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper i husbyggnadsteknik, speciellt beträffande…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten skall tillägna sig kunskaper om laster och krafter i byggkonstruktioner samt gru…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2ME</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NF</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GBY2NF</t>
+          <t>GBY2NG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten skall tillägna sig kunskaper om laster och krafter i byggkonstruktioner samt gru…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om byggandets organisation och genomförand…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GBY2NG</t>
+          <t>GBY2RX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om byggandets organisation och genomförand…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap och…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RX</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GBY2RX</t>
+          <t>GBY2V6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap och…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig grundläggande kunskaper i arbetsplatsens organisat…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GBY2V6</t>
+          <t>GBY2VR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig grundläggande kunskaper i arbetsplatsens organisat…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att öka medvetenheten om de hållbarhetsutmaningar som vi står inför. Kursen avser a…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2VR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GBY2VR</t>
+          <t>GBY2XF</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att öka medvetenheten om de hållbarhetsutmaningar som vi står inför. Kursen avser a…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper i husbyggnadsteknik, speciellt beträffande u…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2VR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2XF</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GBY2XF</t>
+          <t>BFY224</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper i husbyggnadsteknik, speciellt beträffande u…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om vetenskapligt arbetssätt inom naturvetenskap …</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2XF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>BFY224</t>
+          <t>BFY227</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om vetenskapligt arbetssätt inom naturvetenskap …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>BFY225</t>
+          <t>FY1018</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>BFY226</t>
+          <t>GIE26P</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26P</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>BFY227</t>
+          <t>GIE29N</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE29N</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FY1018</t>
+          <t>GIE2L7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2L7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GFY345</t>
+          <t>GIE2MF</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFY345</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2MF</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GIE26L</t>
+          <t>GIE3H2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3H2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GIE26M</t>
+          <t>IE1068</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1068</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GIE26N</t>
+          <t>IE1076</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1351,19 +1351,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1076</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GIE26P</t>
+          <t>IE2003</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': De allmänna målen med examensarbetet är att ge kursdeltagarna möjligheter att utveckla sin förmåga att inom ämnet indust…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE2003</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GIE29N</t>
+          <t>AIK232</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GIE2L7</t>
+          <t>GIK23M</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2L7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GIE2MF</t>
+          <t>GIK289</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2MF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GIE2QS</t>
+          <t>GIK299</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2QS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GIE2RF</t>
+          <t>GIK2AL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2RF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GIE3H2</t>
+          <t>GIK2JX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Efter avslutad kurs ska…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>IE1068</t>
+          <t>GIK2KM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>IE1069</t>
+          <t>GIK2LF</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska den studerande…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2LF</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>IE1076</t>
+          <t>GIK2NV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>IE2003</t>
+          <t>GIK2NX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': De allmänna målen med examensarbetet är att ge kursdeltagarna möjligheter att utveckla sin förmåga att inom ämnet indust…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>AIK232</t>
+          <t>GIK2PB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GIK23M</t>
+          <t>GIK2PD</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till nätverk, nätverkstjänster , nätverkssäkerhet, datakommunikati…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PD</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GIK289</t>
+          <t>GIK2PF</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIK299</t>
+          <t>GIK2PG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIK2AL</t>
+          <t>GIK2V4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GIK2BD</t>
+          <t>GIK2XZ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2BD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIK2FB</t>
+          <t>GIK2YK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YK</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GIK2JX</t>
+          <t>GIK2YL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YL</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GIK2KM</t>
+          <t>GIK2YN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GIK2LF</t>
+          <t>GIK32J</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska studenten kunna:_…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2LF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32J</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GIK2NV</t>
+          <t>GIK347</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska den studenten kunna…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK347</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GIK2NX</t>
+          <t>GIK348</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK348</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GIK2PB</t>
+          <t>IK1032</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska förvärva fördjupade kunskaper inom examensarbetets ämnesområde genom att u…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GIK2PD</t>
+          <t>IK1064</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till nätverk, nätverkstjänster , nätverkssäkerhet, datakommunikati…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig utökade kunskaper i objektorienterad programmering och m…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GIK2PF</t>
+          <t>IK1066</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper och färdigheter inom ämnesområdet geno…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GIK2PG</t>
+          <t>GMA28W</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska …</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GIK2QZ</t>
+          <t>MA0011</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2QZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GIK2UK</t>
+          <t>MA0013</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2UK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GIK2V4</t>
+          <t>MA1040</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska utveckla sin förmåga att förstå och använda matematiska begrepp o…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1040</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GIK2XJ</t>
+          <t>MA1042</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig grundläggande teoretiska kunskaper i elementär a…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GIK2XK</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GIK2XZ</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana ämnes- och ämnesdidaktiska kunskaper som krävs för att i gru…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GIK2YK</t>
+          <t>GMD2AR</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GIK2YL</t>
+          <t>GMD2GF</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GIK2YN</t>
+          <t>GMD2GG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GIK2YP</t>
+          <t>GMD2TV</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GIK2YR</t>
+          <t>GMD2XQ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GIK32J</t>
+          <t>GMD33X</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GIK32K</t>
+          <t>GMD33Y</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse _…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GIK32L</t>
+          <t>MD2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse _…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet för kursen är att den studerande ska vidga och…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GIK32M</t>
+          <t>MT1033</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse _…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter kursen kunna…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GIK32N</t>
+          <t>MT1074</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse _…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig kännedom om och förmåga till analys av de viktigas…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GIK339</t>
+          <t>BEG222</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall ha nått en förtrogenhet med rådande forsknings- och utbildnings…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK339</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GIK346</t>
+          <t>EG1012</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK346</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GIK347</t>
+          <t>EG2004</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK347</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GIK348</t>
+          <t>EG3019</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i …</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK348</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GIK34Y</t>
+          <t>EG3020</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK34Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GIK38G</t>
+          <t>EG3022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK38G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GIK38H</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa och väsentligen fördjupa sina kunskaper inom solenergitekni…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK38H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>IK1032</t>
+          <t>GEG2UE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska förvärva fördjupade kunskaper inom examensarbetets ämnesområde genom att u…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>IK1064</t>
+          <t>GEG2UL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig utökade kunskaper i objektorienterad programmering och m…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>IK1066</t>
+          <t>GEG33B</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper och färdigheter inom ämnesområdet geno…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GMA28W</t>
+          <t>GSQ23J</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillämpa och fördjupa kunskaper och tekniker i databashantering…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>MA0011</t>
+          <t>GSQ25F</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för …</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>MA0013</t>
+          <t>GSQ25J</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>MA1040</t>
+          <t>GSQ25N</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska utveckla sin förmåga att förstå och använda matematiska begrepp o…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>MA1042</t>
+          <t>GSQ2H7</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig grundläggande teoretiska kunskaper i elementär a…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GSQ2LA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>GSQ2PH</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana ämnes- och ämnesdidaktiska kunskaper som krävs för att i gru…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GMD2AR</t>
+          <t>GSQ2R5</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GMD2GF</t>
+          <t>GSQ2Y2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GMD2GG</t>
+          <t>SQ1003</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GMD2TV</t>
+          <t>AMI22Z</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GMD2XQ</t>
+          <t>AMI23J</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GMD33X</t>
+          <t>AMI27V</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GMD33Y</t>
+          <t>AMI295</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>MD2022</t>
+          <t>GMI2C8</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet för kursen är att den studerande ska vidga och…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa …</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GMT343</t>
+          <t>GMI2NW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3214,908 +3214,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska behandla aktiviteter relaterade till automatiska programvarutest …</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>GMT344</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>MTA</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT344</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>GMT349</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>MTA</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT349</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>GMT34R</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>MTA</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>GMT34W</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>MTA</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34W</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>MT1033</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>MTA</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter kursen kunna…</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>MT1074</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>MTA</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig kännedom om och förmåga till analys av de viktigas…</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>BEG222</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall ha nått en förtrogenhet med rådande forsknings- och utbildnings…</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>EG1012</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>EG2004</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>EG3019</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i …</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>EG3020</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>EG3022</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>EG4001</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa och väsentligen fördjupa sina kunskaper inom solenergitekni…</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>GEG2UE</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>GEG2UL</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>GEG33B</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenterna ska efter avslutad kurs kunna:…</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>GSQ23J</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillämpa och fördjupa kunskaper och tekniker i databashantering…</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25F</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för …</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25J</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25N</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2H7</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar…</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2LA</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig…</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2PH</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2R5</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2Y2</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>SQ1003</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>AMI22Z</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>AMI23J</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>AMI27V</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>AMI295</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>GMI2C8</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa …</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>GMI2NW</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska behandla aktiviteter relaterade till automatiska programvarutest …</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2NW</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>GMI35R</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI35R</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E136"/>
+  <autoFilter ref="A1:E103"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4321,72 +3430,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1120,7 +1120,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>BFY227</t>
+          <t>FY1018</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FY1018</t>
+          <t>IE2003</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': De allmänna målen med examensarbetet är att ge kursdeltagarna möjligheter att utveckla sin förmåga att inom ämnet indust…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE2003</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GIE26P</t>
+          <t>GIK23M</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GIE29N</t>
+          <t>GIK299</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GIE2L7</t>
+          <t>GIK2AL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2L7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GIE2MF</t>
+          <t>GIK2KM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2MF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GIE3H2</t>
+          <t>GIK2NV</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>IE1068</t>
+          <t>GIK2NX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>IE1076</t>
+          <t>GIK2PB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>IE2003</t>
+          <t>GIK2PD</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': De allmänna målen med examensarbetet är att ge kursdeltagarna möjligheter att utveckla sin förmåga att inom ämnet indust…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till nätverk, nätverkstjänster , nätverkssäkerhet, datakommunikati…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PD</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>AIK232</t>
+          <t>GIK2PF</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GIK23M</t>
+          <t>GIK2PG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GIK289</t>
+          <t>GIK2V4</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GIK299</t>
+          <t>IK1032</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska förvärva fördjupade kunskaper inom examensarbetets ämnesområde genom att u…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GIK2AL</t>
+          <t>IK1064</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig utökade kunskaper i objektorienterad programmering och m…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GIK2JX</t>
+          <t>IK1066</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Efter avslutad kurs ska…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper och färdigheter inom ämnesområdet geno…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GIK2KM</t>
+          <t>GMA28W</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska …</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GIK2LF</t>
+          <t>MA0011</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter avslutad kurs ska den studerande…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2LF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GIK2NV</t>
+          <t>MA0013</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GIK2NX</t>
+          <t>MA1040</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska utveckla sin förmåga att förstå och använda matematiska begrepp o…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1040</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GIK2PB</t>
+          <t>MA1042</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig grundläggande teoretiska kunskaper i elementär a…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GIK2PD</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till nätverk, nätverkstjänster , nätverkssäkerhet, datakommunikati…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GIK2PF</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana ämnes- och ämnesdidaktiska kunskaper som krävs för att i gru…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIK2PG</t>
+          <t>GMD2AR</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIK2V4</t>
+          <t>GMD2GF</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GIK2XZ</t>
+          <t>GMD2GG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIK2YK</t>
+          <t>GMD2TV</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GIK2YL</t>
+          <t>GMD2XQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GIK2YN</t>
+          <t>GMD33X</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GIK32J</t>
+          <t>GMD33Y</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska studenten kunna:_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GIK347</t>
+          <t>MD2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska den studenten kunna…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet för kursen är att den studerande ska vidga och…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK347</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GIK348</t>
+          <t>MT1033</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter kursen kunna…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK348</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>IK1032</t>
+          <t>MT1074</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska förvärva fördjupade kunskaper inom examensarbetets ämnesområde genom att u…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig kännedom om och förmåga till analys av de viktigas…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>IK1064</t>
+          <t>BEG222</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig utökade kunskaper i objektorienterad programmering och m…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall ha nått en förtrogenhet med rådande forsknings- och utbildnings…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>IK1066</t>
+          <t>EG1012</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper och färdigheter inom ämnesområdet geno…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GMA28W</t>
+          <t>EG2004</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MA0011</t>
+          <t>EG3019</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i …</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>MA0013</t>
+          <t>EG3020</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MA1040</t>
+          <t>EG3022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska utveckla sin förmåga att förstå och använda matematiska begrepp o…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MA1042</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig grundläggande teoretiska kunskaper i elementär a…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa och väsentligen fördjupa sina kunskaper inom solenergitekni…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GEG2UE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>GEG2UL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana ämnes- och ämnesdidaktiska kunskaper som krävs för att i gru…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GMD2AR</t>
+          <t>GEG33B</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GMD2GF</t>
+          <t>GSQ23J</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillämpa och fördjupa kunskaper och tekniker i databashantering…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GMD2GG</t>
+          <t>GSQ25F</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för …</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GMD2TV</t>
+          <t>GSQ25J</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GMD2XQ</t>
+          <t>GSQ25N</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GMD33X</t>
+          <t>GSQ2H7</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GMD33Y</t>
+          <t>GSQ2LA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>MD2022</t>
+          <t>GSQ2PH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet för kursen är att den studerande ska vidga och…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>MT1033</t>
+          <t>GSQ2R5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter kursen kunna…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>MT1074</t>
+          <t>GSQ2Y2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig kännedom om och förmåga till analys av de viktigas…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>BEG222</t>
+          <t>SQ1003</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall ha nått en förtrogenhet med rådande forsknings- och utbildnings…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>EG1012</t>
+          <t>AMI22Z</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>EG2004</t>
+          <t>AMI23J</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>EG3019</t>
+          <t>AMI27V</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>EG3020</t>
+          <t>AMI295</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>EG3022</t>
+          <t>GMI2C8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa …</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>GMI2NW</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,530 +2701,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa och väsentligen fördjupa sina kunskaper inom solenergitekni…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska behandla aktiviteter relaterade till automatiska programvarutest …</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>GEG2UE</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>GEG2UL</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>GEG33B</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenterna ska efter avslutad kurs kunna:…</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>GSQ23J</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillämpa och fördjupa kunskaper och tekniker i databashantering…</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25F</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för …</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25J</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25N</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2H7</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar…</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2LA</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig…</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2PH</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2R5</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2Y2</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>SQ1003</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>AMI22Z</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>AMI23J</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>AMI27V</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>AMI295</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>GMI2C8</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa …</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>GMI2NW</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska behandla aktiviteter relaterade till automatiska programvarutest …</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2NW</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E103"/>
+  <autoFilter ref="A1:E84"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3392,44 +2879,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$G$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>2014-02-20</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper inom samhällsplanering, byggandets regelverk…</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1053</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper inom värme- och fukttransport, ljudisoleri…</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1056</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2015-03-20</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-husmodell.…</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1058</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2015-03-20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall skaffa sig kunskaper om såväl teoretisk som praktisk träbyggnad…</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1059</t>
         </is>
@@ -590,15 +626,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2015-11-23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet me kursen är att studenten ska skaffa sig kunskaper och färdigheter om systemuppbyggnad och funkt…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1061</t>
         </is>
@@ -617,15 +659,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att kursdeltagaren ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformati…</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1065</t>
         </is>
@@ -644,15 +692,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2013-02-21</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2016</t>
         </is>
@@ -671,15 +725,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2016-05-19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska uppnå förmåga att med helhetssyn självständigt och kreativt ident…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2022</t>
         </is>
@@ -698,15 +758,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>2017-04-27</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Vid design av energieffektiva byggnader med hög nivå av komfort och hållbarhet krävs både en djup kunskap om detaljer so…</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3001</t>
         </is>
@@ -725,15 +791,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2017-11-11</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen fokuserar på miljöklassningsverktyg för byggnader. Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3004</t>
         </is>
@@ -752,15 +824,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2020-04-02</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-modell.…</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GB</t>
         </is>
@@ -779,15 +857,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2020-04-02</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformationsmo…</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GC</t>
         </is>
@@ -806,15 +890,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2020-04-30</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper inom fysisk planering med tyng…</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GR</t>
         </is>
@@ -833,15 +923,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>2020-09-03</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska skaffa sig kunskaper…</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2J2</t>
         </is>
@@ -860,15 +956,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om laster och krafter i byggkonstruktioner…</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MA</t>
         </is>
@@ -887,15 +989,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper för att kunna organisera och genomföra pro…</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MB</t>
         </is>
@@ -914,15 +1022,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper i husbyggnadsteknik, speciellt beträffande…</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2ME</t>
         </is>
@@ -941,15 +1055,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten skall tillägna sig kunskaper om laster och krafter i byggkonstruktioner samt gru…</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NF</t>
         </is>
@@ -968,15 +1088,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om byggandets organisation och genomförand…</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NG</t>
         </is>
@@ -995,15 +1121,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap och…</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RX</t>
         </is>
@@ -1022,15 +1154,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig grundläggande kunskaper i arbetsplatsens organisat…</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V6</t>
         </is>
@@ -1049,15 +1187,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att öka medvetenheten om de hållbarhetsutmaningar som vi står inför. Kursen avser a…</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2VR</t>
         </is>
@@ -1076,15 +1220,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2022-09-05</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper i husbyggnadsteknik, speciellt beträffande u…</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2XF</t>
         </is>
@@ -1103,15 +1253,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om vetenskapligt arbetssätt inom naturvetenskap …</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
         </is>
@@ -1130,15 +1286,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
         </is>
@@ -1157,15 +1319,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+          <t>2009-12-08</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': De allmänna målen med examensarbetet är att ge kursdeltagarna möjligheter att utveckla sin förmåga att inom ämnet indust…</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE2003</t>
         </is>
@@ -1184,15 +1352,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
         </is>
@@ -1211,15 +1385,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2019-04-18</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
         </is>
@@ -1238,15 +1418,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
         </is>
@@ -1265,15 +1451,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
         </is>
@@ -1292,15 +1484,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+          <t>2021-03-11</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
         </is>
@@ -1319,15 +1517,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+          <t>2021-03-11</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och…</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
         </is>
@@ -1346,15 +1550,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
         </is>
@@ -1373,15 +1583,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till nätverk, nätverkstjänster , nätverkssäkerhet, datakommunikati…</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PD</t>
         </is>
@@ -1400,15 +1616,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
         </is>
@@ -1427,15 +1649,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
         </is>
@@ -1454,15 +1682,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
         </is>
@@ -1481,15 +1715,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+          <t>2007-06-13</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska förvärva fördjupade kunskaper inom examensarbetets ämnesområde genom att u…</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
         </is>
@@ -1508,15 +1748,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-02-21</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig utökade kunskaper i objektorienterad programmering och m…</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
         </is>
@@ -1535,15 +1785,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2013-03-14</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper och färdigheter inom ämnesområdet geno…</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
         </is>
@@ -1562,15 +1818,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2019-03-21</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska …</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
         </is>
@@ -1589,15 +1851,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+          <t>2013-12-12</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
         </is>
@@ -1616,15 +1884,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>2014-01-30</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
         </is>
@@ -1643,15 +1917,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+          <t>2016-03-24</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska utveckla sin förmåga att förstå och använda matematiska begrepp o…</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1040</t>
         </is>
@@ -1670,15 +1950,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+          <t>2017-02-16</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig grundläggande teoretiska kunskaper i elementär a…</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
@@ -1697,15 +1983,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
@@ -1724,15 +2016,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana ämnes- och ämnesdidaktiska kunskaper som krävs för att i gru…</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
@@ -1751,15 +2049,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2019-08-29</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
         </is>
@@ -1778,15 +2086,25 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2020-04-08</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>2020-12-15</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
@@ -1805,15 +2123,25 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2020-04-08</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>2020-12-15</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
@@ -1832,15 +2160,25 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
         </is>
@@ -1859,15 +2197,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
@@ -1886,15 +2230,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
         </is>
@@ -1913,15 +2263,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
@@ -1940,15 +2296,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet för kursen är att den studerande ska vidga och…</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
@@ -1967,15 +2329,25 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2008-04-29</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>2010-08-26</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter kursen kunna…</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
         </is>
@@ -1994,15 +2366,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+          <t>2018-02-15</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig kännedom om och förmåga till analys av de viktigas…</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
         </is>
@@ -2021,15 +2399,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+          <t>2019-10-17</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall ha nått en förtrogenhet med rådande forsknings- och utbildnings…</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
         </is>
@@ -2048,15 +2432,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+          <t>2017-10-12</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
         </is>
@@ -2075,15 +2465,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+          <t>2015-10-08</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
         </is>
@@ -2102,15 +2498,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+          <t>2017-04-27</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i …</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
         </is>
@@ -2129,15 +2531,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+          <t>2017-12-14</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
         </is>
@@ -2156,15 +2564,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+          <t>2018-01-25</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
         </is>
@@ -2183,15 +2597,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+          <t>2014-11-27</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa och väsentligen fördjupa sina kunskaper inom solenergitekni…</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
@@ -2210,15 +2630,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+          <t>2022-01-27</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
         </is>
@@ -2237,15 +2663,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
         </is>
@@ -2264,15 +2696,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+          <t>2023-02-23</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenterna ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
         </is>
@@ -2291,15 +2729,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+          <t>2018-05-24</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillämpa och fördjupa kunskaper och tekniker i databashantering…</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
         </is>
@@ -2318,15 +2762,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+          <t>2018-10-29</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för …</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
         </is>
@@ -2345,15 +2795,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+          <t>2018-10-29</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
         </is>
@@ -2372,15 +2828,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+          <t>2018-11-08</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
         </is>
@@ -2399,15 +2861,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+          <t>2020-06-29</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar…</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
         </is>
@@ -2426,15 +2894,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig…</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
         </is>
@@ -2453,15 +2927,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
         </is>
@@ -2480,15 +2960,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2021-08-24</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
         </is>
@@ -2507,15 +2993,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
         </is>
@@ -2534,15 +3026,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>2017-10-12</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
         </is>
@@ -2561,15 +3059,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2019-04-18</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
         </is>
@@ -2588,15 +3092,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+          <t>2019-11-07</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
         </is>
@@ -2615,15 +3125,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
         </is>
@@ -2642,15 +3158,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
         </is>
@@ -2669,15 +3191,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+          <t>2019-10-17</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa …</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
         </is>
@@ -2696,189 +3224,195 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+          <t>2021-03-11</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska behandla aktiviteter relaterade till automatiska programvarutest …</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2NW</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E84"/>
+  <autoFilter ref="A1:G84"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$G$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$G$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1243,17 +1243,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>BFY224</t>
+          <t>GDV3KY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>DVE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1264,19 +1264,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om vetenskapligt arbetssätt inom naturvetenskap …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDV3KY</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FY1018</t>
+          <t>BFY224</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1297,29 +1297,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om vetenskapligt arbetssätt inom naturvetenskap …</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>IE2003</t>
+          <t>FY1018</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2009-12-08</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1330,29 +1330,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': De allmänna målen med examensarbetet är att ge kursdeltagarna möjligheter att utveckla sin förmåga att inom ämnet indust…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GIK23M</t>
+          <t>IE2003</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2009-12-08</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1363,19 +1363,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': De allmänna målen med examensarbetet är att ge kursdeltagarna möjligheter att utveckla sin förmåga att inom ämnet indust…</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE2003</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GIK299</t>
+          <t>GIK23M</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2019-04-18</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1396,19 +1396,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GIK2AL</t>
+          <t>GIK299</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2019-08-29</t>
+          <t>2019-04-18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1429,19 +1429,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GIK2KM</t>
+          <t>GIK2AL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2019-08-29</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1462,19 +1462,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GIK2NV</t>
+          <t>GIK2KM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1495,19 +1495,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GIK2NX</t>
+          <t>GIK2NV</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1528,19 +1528,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GIK2PB</t>
+          <t>GIK2NX</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1561,19 +1561,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och…</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GIK2PD</t>
+          <t>GIK2PB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till nätverk, nätverkstjänster , nätverkssäkerhet, datakommunikati…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GIK2PF</t>
+          <t>GIK2PD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1627,19 +1627,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till nätverk, nätverkstjänster , nätverkssäkerhet, datakommunikati…</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PD</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GIK2PG</t>
+          <t>GIK2PF</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1660,19 +1660,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GIK2V4</t>
+          <t>GIK2PG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1693,19 +1693,19 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>IK1032</t>
+          <t>GIK2V4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2007-06-13</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1726,19 +1726,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska förvärva fördjupade kunskaper inom examensarbetets ämnesområde genom att u…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>IK1064</t>
+          <t>IK1032</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1748,14 +1748,10 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2013-02-21</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
+          <t>2007-06-13</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -1763,19 +1759,19 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig utökade kunskaper i objektorienterad programmering och m…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska förvärva fördjupade kunskaper inom examensarbetets ämnesområde genom att u…</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>IK1066</t>
+          <t>IK1064</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1785,10 +1781,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2013-03-14</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>2013-02-21</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -1796,29 +1796,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper och färdigheter inom ämnesområdet geno…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig utökade kunskaper i objektorienterad programmering och m…</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GMA28W</t>
+          <t>IK1066</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2019-03-21</t>
+          <t>2013-03-14</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1829,19 +1829,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper och färdigheter inom ämnesområdet geno…</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MA0011</t>
+          <t>GMA28W</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2013-12-12</t>
+          <t>2019-03-21</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1862,19 +1862,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska …</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MA0013</t>
+          <t>MA0011</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2014-01-30</t>
+          <t>2013-12-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1900,14 +1900,14 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MA1040</t>
+          <t>MA0013</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2016-03-24</t>
+          <t>2014-01-30</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1928,19 +1928,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska utveckla sin förmåga att förstå och använda matematiska begrepp o…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.…</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MA1042</t>
+          <t>MA1040</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2017-02-16</t>
+          <t>2016-03-24</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1961,29 +1961,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig grundläggande teoretiska kunskaper i elementär a…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska utveckla sin förmåga att förstå och använda matematiska begrepp o…</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1040</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>MA1042</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
+          <t>2017-02-16</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1994,19 +1994,19 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig grundläggande teoretiska kunskaper i elementär a…</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2027,19 +2027,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana ämnes- och ämnesdidaktiska kunskaper som krävs för att i gru…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GMD2AR</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2049,14 +2049,10 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2019-08-29</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2021-12-03</t>
-        </is>
-      </c>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2064,19 +2060,19 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande visar sådana ämnes- och ämnesdidaktiska kunskaper som krävs för att i gru…</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GMD2GF</t>
+          <t>GMD2AR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2086,12 +2082,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2020-04-08</t>
+          <t>2019-08-29</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2020-12-15</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2101,19 +2097,19 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GMD2GG</t>
+          <t>GMD2GF</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2143,14 +2139,14 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GMD2TV</t>
+          <t>GMD2GG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2160,12 +2156,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
+          <t>2020-04-08</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2175,19 +2171,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten utvecklar och fördjupar sina matematiska och matematikdidaktiska kunskaper för…</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GMD2XQ</t>
+          <t>GMD2TV</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2197,10 +2193,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>2021-12-22</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2208,19 +2208,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar och fördjupar sina matematiska förmågor och kunskaper samtidigt…</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GMD33X</t>
+          <t>GMD2XQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2023-03-17</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2241,19 +2241,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GMD33Y</t>
+          <t>GMD33X</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2274,19 +2274,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>MD2022</t>
+          <t>GMD33Y</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2017-09-28</t>
+          <t>2023-03-17</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2307,36 +2307,32 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet för kursen är att den studerande ska vidga och…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar och fördjupar sina matematiska förmågor och sina kunskaper i mat…</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>MT1033</t>
+          <t>MD2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2008-04-29</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2010-08-26</t>
-        </is>
-      </c>
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2344,19 +2340,19 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter kursen kunna…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet för kursen är att den studerande ska vidga och…</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>MT1074</t>
+          <t>MT1033</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2366,10 +2362,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2018-02-15</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>2008-04-29</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2010-08-26</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2377,29 +2377,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig kännedom om och förmåga till analys av de viktigas…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter kursen kunna…</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>BEG222</t>
+          <t>MT1074</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2019-10-17</t>
+          <t>2018-02-15</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -2410,19 +2410,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall ha nått en förtrogenhet med rådande forsknings- och utbildnings…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig kännedom om och förmåga till analys av de viktigas…</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>EG1012</t>
+          <t>BEG222</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2017-10-12</t>
+          <t>2019-10-17</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -2443,19 +2443,19 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall ha nått en förtrogenhet med rådande forsknings- och utbildnings…</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>EG2004</t>
+          <t>EG1012</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2017-10-12</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -2476,19 +2476,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>EG3019</t>
+          <t>EG2004</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2017-04-27</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -2509,19 +2509,19 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>EG3020</t>
+          <t>EG3019</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2017-12-14</t>
+          <t>2017-04-27</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -2542,19 +2542,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i …</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>EG3022</t>
+          <t>EG3020</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2018-01-25</t>
+          <t>2017-12-14</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2575,19 +2575,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>EG3022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2014-11-27</t>
+          <t>2018-01-25</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2608,19 +2608,19 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa och väsentligen fördjupa sina kunskaper inom solenergitekni…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GEG2UE</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2022-01-27</t>
+          <t>2014-11-27</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2641,19 +2641,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med examensarbetet är att studenten ska kunna tillämpa och väsentligen fördjupa sina kunskaper inom solenergitekni…</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GEG2UL</t>
+          <t>GEG2UE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-01-27</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2674,19 +2674,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter genomgången kurs kunna…</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GEG33B</t>
+          <t>GEG2UL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2707,29 +2707,29 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenterna ska efter avslutad kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GSQ23J</t>
+          <t>GEG33B</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2018-05-24</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -2740,19 +2740,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillämpa och fördjupa kunskaper och tekniker i databashantering…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSQ25F</t>
+          <t>GSQ23J</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2018-10-29</t>
+          <t>2018-05-24</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -2773,19 +2773,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillämpa och fördjupa kunskaper och tekniker i databashantering…</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSQ25J</t>
+          <t>GSQ25F</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för …</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSQ25N</t>
+          <t>GSQ25J</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2018-11-08</t>
+          <t>2018-10-29</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -2839,19 +2839,19 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GSQ2H7</t>
+          <t>GSQ25N</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2018-11-08</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -2872,19 +2872,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GSQ2LA</t>
+          <t>GSQ2H7</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2020-06-29</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2905,19 +2905,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar…</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GSQ2PH</t>
+          <t>GSQ2LA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2938,19 +2938,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig…</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GSQ2R5</t>
+          <t>GSQ2PH</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2971,19 +2971,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSQ2Y2</t>
+          <t>GSQ2R5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -3004,19 +3004,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SQ1003</t>
+          <t>GSQ2Y2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2017-10-12</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3037,29 +3037,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>AMI22Z</t>
+          <t>SQ1003</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2019-04-18</t>
+          <t>2017-10-12</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3070,19 +3070,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AMI23J</t>
+          <t>AMI22Z</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2019-11-07</t>
+          <t>2019-04-18</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -3103,19 +3103,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>AMI27V</t>
+          <t>AMI23J</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2019-11-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3136,19 +3136,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>AMI295</t>
+          <t>AMI27V</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -3169,19 +3169,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GMI2C8</t>
+          <t>AMI295</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2019-10-17</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -3202,19 +3202,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GMI2NW</t>
+          <t>GMI2C8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2019-10-17</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -3235,17 +3235,50 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa …</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>GMI2NW</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2021-03-11</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska behandla aktiviteter relaterade till automatiska programvarutest …</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2NW</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G84"/>
+  <autoFilter ref="A1:G85"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -3413,6 +3446,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
